--- a/config/lista_toxiner.xlsx
+++ b/config/lista_toxiner.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\SLV-Biotoxin-Validator-App\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F539842F-4F07-4E75-B985-A69121A2F8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5DA811-D6B1-482B-AB9C-E7AF0AA9B08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5EE10D2C-8E1B-4393-ADF2-C1365B6C7898}"/>
+    <workbookView xWindow="25490" yWindow="0" windowWidth="25820" windowHeight="13900" xr2:uid="{5EE10D2C-8E1B-4393-ADF2-C1365B6C7898}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$AG$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$AI$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="419">
   <si>
     <t>Enhet</t>
   </si>
@@ -1233,6 +1233,72 @@
   </si>
   <si>
     <t>AZA total</t>
+  </si>
+  <si>
+    <t>NERC_vocab_S27</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004031/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004222/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004216/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004128/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004223/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004046/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS003969/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004206/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004224/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004047/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004013/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004011/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004220/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004030/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004234/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004033/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004037/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004038/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004035/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004036/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004059/</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1379,7 +1445,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1704,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604718B0-4585-451D-AFD3-6923AD565DA1}">
-  <dimension ref="A1:AG72"/>
+  <dimension ref="A1:AI72"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.26953125" bestFit="1" customWidth="1"/>
@@ -1724,23 +1789,24 @@
     <col min="16" max="16" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="21.26953125" customWidth="1"/>
     <col min="19" max="19" width="46.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7265625" customWidth="1"/>
-    <col min="21" max="21" width="8.1796875" customWidth="1"/>
-    <col min="22" max="22" width="6.7265625" customWidth="1"/>
-    <col min="23" max="23" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="27.453125" customWidth="1"/>
-    <col min="26" max="26" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="53.7265625" customWidth="1"/>
-    <col min="28" max="28" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="26.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.26953125" customWidth="1"/>
-    <col min="33" max="33" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7265625" customWidth="1"/>
+    <col min="22" max="22" width="8.1796875" customWidth="1"/>
+    <col min="23" max="23" width="6.7265625" customWidth="1"/>
+    <col min="24" max="24" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.453125" customWidth="1"/>
+    <col min="27" max="27" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="53.7265625" customWidth="1"/>
+    <col min="29" max="29" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.26953125" customWidth="1"/>
+    <col min="35" max="35" width="29.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -1753,25 +1819,25 @@
       <c r="D1" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="17" t="s">
         <v>370</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -1798,50 +1864,53 @@
       <c r="S1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>25</v>
       </c>
@@ -1883,37 +1952,38 @@
       <c r="S2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="12" t="s">
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AF2" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="AE2" s="4" t="s">
+      <c r="AG2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AH2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="AG2" t="str">
-        <f t="shared" ref="AG2:AG33" si="0">CONCATENATE(AC2, " (", AE2, ")")</f>
+      <c r="AI2" t="str">
+        <f t="shared" ref="AI2:AI33" si="0">CONCATENATE(AE2, " (", AG2, ")")</f>
         <v>E_coli (cells/100 g)</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1949,7 +2019,7 @@
       <c r="O3" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="P3" s="22"/>
+      <c r="P3" s="21"/>
       <c r="Q3" s="4" t="s">
         <v>88</v>
       </c>
@@ -1959,47 +2029,50 @@
       <c r="S3" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="U3" s="4">
+      <c r="V3" s="4">
         <v>30</v>
       </c>
-      <c r="V3" s="4"/>
       <c r="W3" s="4"/>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="AA3" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AA3" s="20" t="s">
+      <c r="AB3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="AB3" s="5">
+      <c r="AC3" s="5">
         <v>45691</v>
       </c>
-      <c r="AC3" s="12" t="s">
+      <c r="AD3" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="AE3" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="AD3" s="12" t="s">
+      <c r="AF3" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AG3" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AH3" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="AG3" t="str">
+      <c r="AI3" t="str">
         <f t="shared" si="0"/>
         <v>AZA1 (ug AZA eq/kg)</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2035,7 +2108,7 @@
       <c r="O4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="P4" s="23" t="s">
+      <c r="P4" s="22" t="s">
         <v>373</v>
       </c>
       <c r="Q4" s="4" t="s">
@@ -2047,47 +2120,50 @@
       <c r="S4" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="U4" s="4">
+      <c r="V4" s="4">
         <v>30</v>
       </c>
-      <c r="V4" s="4"/>
       <c r="W4" s="4"/>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="AA4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>77</v>
       </c>
-      <c r="AB4" s="5">
+      <c r="AC4" s="5">
         <v>45691</v>
       </c>
-      <c r="AC4" s="12" t="s">
+      <c r="AD4" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="AE4" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="AD4" s="12" t="s">
+      <c r="AF4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="AG4" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AH4" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="AG4" t="str">
+      <c r="AI4" t="str">
         <f t="shared" si="0"/>
         <v>AZA2 (ug AZA eq/kg)</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2123,7 +2199,7 @@
       <c r="O5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="P5" s="22" t="s">
+      <c r="P5" s="21" t="s">
         <v>374</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -2135,47 +2211,50 @@
       <c r="S5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="U5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="U5" s="4">
+      <c r="V5" s="4">
         <v>30</v>
       </c>
-      <c r="V5" s="4"/>
       <c r="W5" s="4"/>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="AA5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AB5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AC5" s="5">
         <v>45691</v>
       </c>
-      <c r="AC5" s="12" t="s">
+      <c r="AD5" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="AE5" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="AD5" s="12" t="s">
+      <c r="AF5" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="AE5" s="4" t="s">
+      <c r="AG5" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AH5" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="AG5" t="str">
+      <c r="AI5" t="str">
         <f t="shared" si="0"/>
         <v>AZA3 (ug AZA eq/kg)</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -2221,43 +2300,44 @@
       <c r="S6" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T6" s="4" t="s">
+      <c r="U6" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="U6" s="4">
+      <c r="V6" s="4">
         <v>30</v>
       </c>
-      <c r="V6" s="4">
+      <c r="W6" s="4">
         <v>160</v>
       </c>
-      <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="Z6" s="4" t="s">
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="5">
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="5">
         <v>45691</v>
       </c>
-      <c r="AC6" s="12" t="s">
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="AD6" s="12" t="s">
+      <c r="AF6" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="AE6" s="4" t="s">
+      <c r="AG6" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="AF6" s="4" t="s">
+      <c r="AH6" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="AG6" t="str">
+      <c r="AI6" t="str">
         <f t="shared" si="0"/>
         <v>AZA_tot (ug AZA eq/kg)</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>1</v>
       </c>
@@ -2293,7 +2373,7 @@
       <c r="O7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="22" t="s">
+      <c r="P7" s="21" t="s">
         <v>375</v>
       </c>
       <c r="Q7" s="12" t="s">
@@ -2305,51 +2385,54 @@
       <c r="S7" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="U7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="12">
+      <c r="V7" s="12">
         <v>3</v>
       </c>
-      <c r="V7" s="12">
+      <c r="W7" s="12">
         <v>20</v>
       </c>
-      <c r="W7" s="12">
+      <c r="X7" s="12">
         <v>1</v>
       </c>
-      <c r="X7" s="12" t="s">
+      <c r="Y7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="Y7" s="12" t="s">
+      <c r="Z7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Z7" s="12" t="s">
+      <c r="AA7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AA7" s="16" t="s">
+      <c r="AB7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AB7" s="15">
+      <c r="AC7" s="5">
         <v>45688</v>
       </c>
-      <c r="AC7" s="12" t="s">
+      <c r="AD7" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AD7" s="12" t="s">
+      <c r="AF7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="AE7" s="12" t="s">
+      <c r="AG7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AF7" s="12" t="s">
+      <c r="AH7" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="AG7" s="14" t="str">
+      <c r="AI7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>DA (mg/kg)</v>
       </c>
     </row>
-    <row r="8" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>167</v>
       </c>
@@ -2389,7 +2472,6 @@
         <v>47</v>
       </c>
       <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
@@ -2397,25 +2479,29 @@
       <c r="Y8" s="12"/>
       <c r="Z8" s="12"/>
       <c r="AA8" s="12"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="12" t="s">
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE8" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="AD8" s="12" t="s">
+      <c r="AF8" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="AE8" s="12" t="s">
+      <c r="AG8" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AF8" s="12" t="s">
+      <c r="AH8" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AG8" s="14" t="str">
+      <c r="AI8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>DA_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="9" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>10</v>
       </c>
@@ -2461,37 +2547,40 @@
       <c r="S9" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="T9" s="24"/>
-      <c r="U9" s="12"/>
+      <c r="U9" s="23"/>
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
       <c r="Y9" s="12"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="16" t="s">
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AB9" s="15">
+      <c r="AC9" s="5">
         <v>45691</v>
       </c>
-      <c r="AC9" s="12" t="s">
+      <c r="AD9" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE9" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="AD9" s="12" t="s">
+      <c r="AF9" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="AE9" s="12" t="s">
+      <c r="AG9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AF9" s="12" t="s">
+      <c r="AH9" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="AG9" s="14" t="str">
+      <c r="AI9" s="14" t="str">
         <f t="shared" si="0"/>
         <v>DA_screening (mg/kg)</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -2537,42 +2626,43 @@
       <c r="S10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="U10" s="4">
+      <c r="V10" s="4">
         <v>30</v>
       </c>
-      <c r="V10" s="4">
+      <c r="W10" s="4">
         <v>160</v>
       </c>
-      <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="4" t="s">
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AB10" s="5">
+      <c r="AC10" s="5">
         <v>45691</v>
       </c>
-      <c r="AC10" s="12" t="s">
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="AD10" s="12" t="s">
+      <c r="AF10" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="AE10" s="4" t="s">
+      <c r="AG10" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF10" s="4" t="s">
+      <c r="AH10" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG10" t="str">
+      <c r="AI10" t="str">
         <f t="shared" si="0"/>
         <v>DST_tot (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2608,7 +2698,7 @@
       <c r="O11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="P11" s="22" t="s">
+      <c r="P11" s="21" t="s">
         <v>376</v>
       </c>
       <c r="Q11" s="4" t="s">
@@ -2620,47 +2710,50 @@
       <c r="S11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="U11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="U11" s="4">
+      <c r="V11" s="4">
         <v>30</v>
       </c>
-      <c r="V11" s="4"/>
       <c r="W11" s="4"/>
-      <c r="X11" s="4" t="s">
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="Y11" s="4" t="s">
+      <c r="Z11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z11" s="4" t="s">
+      <c r="AA11" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AA11" s="20" t="s">
+      <c r="AB11" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="AB11" s="5">
+      <c r="AC11" s="5">
         <v>45691</v>
       </c>
-      <c r="AC11" s="12" t="s">
+      <c r="AD11" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="AE11" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AD11" s="12" t="s">
+      <c r="AF11" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AE11" s="4" t="s">
+      <c r="AG11" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF11" s="4" t="s">
+      <c r="AH11" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG11" t="str">
+      <c r="AI11" t="str">
         <f t="shared" si="0"/>
         <v>DTX1 (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -2706,47 +2799,48 @@
       <c r="S12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T12" s="4" t="s">
+      <c r="U12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="U12" s="4">
+      <c r="V12" s="4">
         <v>30</v>
       </c>
-      <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="4" t="s">
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="Z12" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="AA12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AA12" s="20" t="s">
+      <c r="AB12" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="AB12" s="5">
+      <c r="AC12" s="5">
         <v>45691</v>
       </c>
-      <c r="AC12" s="12" t="s">
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AD12" s="12" t="s">
+      <c r="AF12" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="AE12" s="4" t="s">
+      <c r="AG12" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF12" s="4" t="s">
+      <c r="AH12" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG12" t="str">
+      <c r="AI12" t="str">
         <f t="shared" si="0"/>
         <v>DTX3 (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -2782,7 +2876,7 @@
       <c r="O13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="P13" s="22" t="s">
+      <c r="P13" s="21" t="s">
         <v>377</v>
       </c>
       <c r="Q13" s="4" t="s">
@@ -2794,47 +2888,50 @@
       <c r="S13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T13" s="4" t="s">
+      <c r="U13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="U13" s="4">
+      <c r="V13" s="4">
         <v>30</v>
       </c>
-      <c r="V13" s="4"/>
       <c r="W13" s="4"/>
-      <c r="X13" s="4" t="s">
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="Y13" s="4" t="s">
+      <c r="Z13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="AA13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AA13" s="20" t="s">
+      <c r="AB13" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="AB13" s="5">
+      <c r="AC13" s="5">
         <v>45691</v>
       </c>
-      <c r="AC13" s="12" t="s">
+      <c r="AD13" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="AE13" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AD13" s="12" t="s">
+      <c r="AF13" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AE13" s="4" t="s">
+      <c r="AG13" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF13" s="4" t="s">
+      <c r="AH13" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG13" t="str">
+      <c r="AI13" t="str">
         <f t="shared" si="0"/>
         <v>DTX2 (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
@@ -2880,40 +2977,41 @@
       <c r="S14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="U14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="U14" s="4">
+      <c r="V14" s="4">
         <v>30</v>
       </c>
-      <c r="V14" s="4"/>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-      <c r="Z14" s="4" t="s">
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AB14" s="5">
+      <c r="AC14" s="5">
         <v>45691</v>
       </c>
-      <c r="AC14" s="12" t="s">
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="AD14" s="12" t="s">
+      <c r="AF14" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="AE14" s="4" t="s">
+      <c r="AG14" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF14" s="4" t="s">
+      <c r="AH14" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG14" t="str">
+      <c r="AI14" t="str">
         <f t="shared" si="0"/>
         <v>DTX2_acyl (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -2959,41 +3057,42 @@
       <c r="S15" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T15" s="4" t="s">
+      <c r="U15" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="U15" s="4">
+      <c r="V15" s="4">
         <v>30</v>
       </c>
-      <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-      <c r="Z15" s="4" t="s">
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="5">
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="5">
         <v>45691</v>
       </c>
-      <c r="AC15" s="12" t="s">
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AD15" s="12" t="s">
+      <c r="AF15" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="AE15" s="4" t="s">
+      <c r="AG15" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF15" s="4" t="s">
+      <c r="AH15" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG15" t="str">
+      <c r="AI15" t="str">
         <f t="shared" si="0"/>
         <v>OA_acyl (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -3029,7 +3128,7 @@
       <c r="O16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="P16" s="22" t="s">
+      <c r="P16" s="21" t="s">
         <v>378</v>
       </c>
       <c r="Q16" s="4" t="s">
@@ -3041,49 +3140,50 @@
       <c r="S16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T16" s="4" t="s">
+      <c r="U16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="U16" s="4">
+      <c r="V16" s="4">
         <v>30</v>
       </c>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4">
+      <c r="W16" s="4"/>
+      <c r="X16" s="4">
         <v>1</v>
-      </c>
-      <c r="X16" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="Y16" s="4" t="s">
         <v>93</v>
       </c>
       <c r="Z16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA16" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AA16" s="20" t="s">
+      <c r="AB16" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AB16" s="5">
+      <c r="AC16" s="5">
         <v>45691</v>
       </c>
-      <c r="AC16" s="12" t="s">
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AD16" s="12" t="s">
+      <c r="AF16" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AE16" s="4" t="s">
+      <c r="AG16" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AF16" s="4" t="s">
+      <c r="AH16" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AG16" t="str">
+      <c r="AI16" t="str">
         <f t="shared" si="0"/>
         <v>Okadaic acid (ug OA eq/kg)</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -3119,7 +3219,7 @@
       <c r="O17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="P17" s="22" t="s">
+      <c r="P17" s="21" t="s">
         <v>379</v>
       </c>
       <c r="Q17" s="4" t="s">
@@ -3131,47 +3231,50 @@
       <c r="S17" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="T17" s="4" t="s">
+      <c r="U17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="U17" s="4">
+      <c r="V17" s="4">
         <v>30</v>
       </c>
-      <c r="V17" s="4"/>
       <c r="W17" s="4"/>
-      <c r="X17" s="4" t="s">
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="Y17" s="4" t="s">
+      <c r="Z17" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="Z17" s="4" t="s">
+      <c r="AA17" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA17" s="20" t="s">
+      <c r="AB17" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="AB17" s="5">
+      <c r="AC17" s="5">
         <v>45691</v>
       </c>
-      <c r="AC17" s="12" t="s">
+      <c r="AD17" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="AE17" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="AD17" s="12" t="s">
+      <c r="AF17" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="AE17" s="4" t="s">
+      <c r="AG17" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="AF17" s="4" t="s">
+      <c r="AH17" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="AG17" t="str">
+      <c r="AI17" t="str">
         <f t="shared" si="0"/>
         <v>PTX1 (ug PTX eq/kg)</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
@@ -3207,7 +3310,7 @@
       <c r="O18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="P18" s="22" t="s">
+      <c r="P18" s="21" t="s">
         <v>380</v>
       </c>
       <c r="Q18" s="4" t="s">
@@ -3219,47 +3322,50 @@
       <c r="S18" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="T18" s="4" t="s">
+      <c r="U18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="U18" s="4">
+      <c r="V18" s="4">
         <v>30</v>
       </c>
-      <c r="V18" s="4"/>
       <c r="W18" s="4"/>
-      <c r="X18" s="4" t="s">
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="Y18" s="4" t="s">
+      <c r="Z18" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="Z18" s="4" t="s">
+      <c r="AA18" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA18" s="20" t="s">
+      <c r="AB18" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="AB18" s="5">
+      <c r="AC18" s="5">
         <v>45691</v>
       </c>
-      <c r="AC18" s="12" t="s">
+      <c r="AD18" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="AE18" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="AD18" s="12" t="s">
+      <c r="AF18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="AE18" s="4" t="s">
+      <c r="AG18" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="AF18" s="4" t="s">
+      <c r="AH18" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="AG18" t="str">
+      <c r="AI18" t="str">
         <f t="shared" si="0"/>
         <v>PTX2 (ug PTX eq/kg)</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -3305,41 +3411,42 @@
       <c r="S19" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="T19" s="4" t="s">
+      <c r="U19" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="4">
+      <c r="V19" s="4">
         <v>30</v>
       </c>
-      <c r="V19" s="4"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
-      <c r="Z19" s="4" t="s">
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="5">
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="5">
         <v>45691</v>
       </c>
-      <c r="AC19" s="12" t="s">
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="AD19" s="12" t="s">
+      <c r="AF19" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="AE19" s="4" t="s">
+      <c r="AG19" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="AF19" s="4" t="s">
+      <c r="AH19" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="AG19" t="str">
+      <c r="AI19" t="str">
         <f t="shared" si="0"/>
         <v>PTX_tot (ug PTX eq/kg)</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>156</v>
       </c>
@@ -3379,37 +3486,38 @@
       <c r="S20" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T20" s="6" t="s">
+      <c r="U20" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
-      <c r="Z20" s="4" t="s">
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="12" t="s">
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="AD20" s="12" t="s">
+      <c r="AF20" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="AE20" s="4" t="s">
+      <c r="AG20" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF20" s="4" t="s">
+      <c r="AH20" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG20" t="str">
+      <c r="AI20" t="str">
         <f t="shared" si="0"/>
         <v>C1_2 (true or false)</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>26</v>
       </c>
@@ -3445,7 +3553,7 @@
       <c r="O21" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P21" s="22"/>
+      <c r="P21" s="21"/>
       <c r="Q21" s="4" t="s">
         <v>117</v>
       </c>
@@ -3455,47 +3563,48 @@
       <c r="S21" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T21" s="4" t="s">
+      <c r="U21" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="U21" s="4">
+      <c r="V21" s="4">
         <v>40</v>
       </c>
-      <c r="V21" s="4"/>
       <c r="W21" s="4"/>
-      <c r="X21" s="4" t="s">
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="Y21" s="4" t="s">
+      <c r="Z21" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="Z21" s="4" t="s">
+      <c r="AA21" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA21" s="20" t="s">
+      <c r="AB21" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="AB21" s="5">
+      <c r="AC21" s="5">
         <v>45691</v>
       </c>
-      <c r="AC21" s="12" t="s">
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="AD21" s="12" t="s">
+      <c r="AF21" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="AE21" s="4" t="s">
+      <c r="AG21" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF21" s="4" t="s">
+      <c r="AH21" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG21" t="str">
+      <c r="AI21" t="str">
         <f t="shared" si="0"/>
         <v>STX_C1_C2 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="22" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>168</v>
       </c>
@@ -3529,32 +3638,34 @@
         <v>117</v>
       </c>
       <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="12" t="s">
+      <c r="AA22" s="12"/>
+      <c r="AB22"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="AD22" s="12" t="s">
+      <c r="AF22" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="AE22" s="12" t="s">
+      <c r="AG22" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AF22" s="12" t="s">
+      <c r="AH22" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AG22" s="14" t="str">
+      <c r="AI22" s="14" t="str">
         <f t="shared" si="0"/>
         <v>C3_4 (true or false)</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>27</v>
       </c>
@@ -3600,45 +3711,46 @@
       <c r="S23" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T23" s="4" t="s">
+      <c r="U23" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="Y23" s="4" t="s">
+      <c r="Z23" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="Z23" s="4" t="s">
+      <c r="AA23" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>122</v>
       </c>
-      <c r="AB23" s="5">
+      <c r="AC23" s="5">
         <v>45691</v>
       </c>
-      <c r="AC23" s="12" t="s">
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="AD23" s="12" t="s">
+      <c r="AF23" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="AE23" s="4" t="s">
+      <c r="AG23" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF23" s="4" t="s">
+      <c r="AH23" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG23" t="str">
+      <c r="AI23" t="str">
         <f t="shared" si="0"/>
         <v>STX_C3_C4 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>163</v>
       </c>
@@ -3662,37 +3774,37 @@
       <c r="M24" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="P24" s="21"/>
+      <c r="P24" s="20"/>
       <c r="Q24" s="4" t="s">
         <v>117</v>
       </c>
       <c r="R24" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="T24" s="4" t="s">
+      <c r="U24" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="Z24" s="4" t="s">
+      <c r="AA24" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AC24" s="12" t="s">
+      <c r="AE24" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="AD24" s="12" t="s">
+      <c r="AF24" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="AE24" s="4" t="s">
+      <c r="AG24" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF24" s="4" t="s">
+      <c r="AH24" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG24" t="str">
+      <c r="AI24" t="str">
         <f t="shared" si="0"/>
         <v>dcGTX2_3_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>28</v>
       </c>
@@ -3728,7 +3840,7 @@
       <c r="O25" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P25" s="23"/>
+      <c r="P25" s="22"/>
       <c r="Q25" s="4" t="s">
         <v>117</v>
       </c>
@@ -3738,47 +3850,48 @@
       <c r="S25" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T25" s="4" t="s">
+      <c r="U25" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="U25" s="4">
+      <c r="V25" s="4">
         <v>125</v>
       </c>
-      <c r="V25" s="4"/>
       <c r="W25" s="4"/>
-      <c r="X25" s="4" t="s">
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Y25" s="4" t="s">
+      <c r="Z25" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="Z25" s="4" t="s">
+      <c r="AA25" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA25" s="20" t="s">
+      <c r="AB25" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="AB25" s="5">
+      <c r="AC25" s="5">
         <v>45691</v>
       </c>
-      <c r="AC25" s="12" t="s">
+      <c r="AD25" s="5"/>
+      <c r="AE25" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="AD25" s="12" t="s">
+      <c r="AF25" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="AE25" s="4" t="s">
+      <c r="AG25" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF25" s="4" t="s">
+      <c r="AH25" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG25" t="str">
+      <c r="AI25" t="str">
         <f t="shared" si="0"/>
         <v>dcGTX2_dcGTX3 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>165</v>
       </c>
@@ -3802,37 +3915,37 @@
       <c r="M26" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="P26" s="21"/>
+      <c r="P26" s="20"/>
       <c r="Q26" s="4" t="s">
         <v>117</v>
       </c>
       <c r="R26" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="T26" s="4" t="s">
+      <c r="U26" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="Z26" s="4" t="s">
+      <c r="AA26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AC26" s="12" t="s">
+      <c r="AE26" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="AD26" s="12" t="s">
+      <c r="AF26" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="AE26" s="4" t="s">
+      <c r="AG26" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF26" s="4" t="s">
+      <c r="AH26" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG26" t="str">
+      <c r="AI26" t="str">
         <f t="shared" si="0"/>
         <v>dcNEO_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -3868,7 +3981,7 @@
       <c r="O27" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P27" s="22" t="s">
+      <c r="P27" s="21" t="s">
         <v>383</v>
       </c>
       <c r="Q27" s="4" t="s">
@@ -3880,47 +3993,48 @@
       <c r="S27" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T27" s="4" t="s">
+      <c r="U27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="U27" s="4">
+      <c r="V27" s="4">
         <v>160</v>
       </c>
-      <c r="V27" s="4"/>
       <c r="W27" s="4"/>
-      <c r="X27" s="4" t="s">
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="Y27" s="4" t="s">
+      <c r="Z27" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Z27" s="4" t="s">
+      <c r="AA27" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA27" s="20" t="s">
+      <c r="AB27" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="AB27" s="5">
+      <c r="AC27" s="5">
         <v>45691</v>
       </c>
-      <c r="AC27" s="12" t="s">
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="AD27" s="12" t="s">
+      <c r="AF27" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="AE27" s="4" t="s">
+      <c r="AG27" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF27" s="4" t="s">
+      <c r="AH27" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG27" t="str">
+      <c r="AI27" t="str">
         <f t="shared" si="0"/>
         <v>dcNeoSTX (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="28" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>30</v>
       </c>
@@ -3954,33 +4068,36 @@
         <v>117</v>
       </c>
       <c r="S28" s="12"/>
-      <c r="T28" s="12" t="s">
+      <c r="U28" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="U28" s="12"/>
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
-      <c r="Z28" s="12" t="s">
+      <c r="X28" s="12"/>
+      <c r="AA28" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="AC28" s="12" t="s">
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="AD28" s="12" t="s">
+      <c r="AF28" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="AE28" s="12" t="s">
+      <c r="AG28" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AF28" s="12" t="s">
+      <c r="AH28" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AG28" s="14" t="str">
+      <c r="AI28" s="14" t="str">
         <f t="shared" si="0"/>
         <v>dcSTX_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -4016,7 +4133,7 @@
       <c r="O29" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P29" s="22" t="s">
+      <c r="P29" s="21" t="s">
         <v>384</v>
       </c>
       <c r="Q29" s="4" t="s">
@@ -4028,47 +4145,48 @@
       <c r="S29" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T29" s="4" t="s">
+      <c r="U29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="U29" s="4">
+      <c r="V29" s="4">
         <v>41</v>
       </c>
-      <c r="V29" s="4"/>
       <c r="W29" s="4"/>
-      <c r="X29" s="4" t="s">
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Y29" s="4" t="s">
+      <c r="Z29" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="Z29" s="4" t="s">
+      <c r="AA29" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA29" s="20" t="s">
+      <c r="AB29" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="AB29" s="5">
+      <c r="AC29" s="5">
         <v>45691</v>
       </c>
-      <c r="AC29" s="12" t="s">
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AD29" s="12" t="s">
+      <c r="AF29" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AE29" s="4" t="s">
+      <c r="AG29" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF29" s="4" t="s">
+      <c r="AH29" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG29" t="str">
+      <c r="AI29" t="str">
         <f t="shared" si="0"/>
         <v>dcSTX (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>33</v>
       </c>
@@ -4102,37 +4220,38 @@
         <v>117</v>
       </c>
       <c r="S30" s="4"/>
-      <c r="T30" s="4" t="s">
+      <c r="U30" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="U30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
-      <c r="Z30" s="4" t="s">
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="5"/>
-      <c r="AC30" s="12" t="s">
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="AD30" s="12" t="s">
+      <c r="AF30" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="AE30" s="4" t="s">
+      <c r="AG30" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF30" s="4" t="s">
+      <c r="AH30" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG30" t="str">
+      <c r="AI30" t="str">
         <f t="shared" si="0"/>
         <v>GTX1_4_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>32</v>
       </c>
@@ -4178,47 +4297,48 @@
       <c r="S31" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T31" s="4" t="s">
+      <c r="U31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="U31" s="4">
+      <c r="V31" s="4">
         <v>330</v>
       </c>
-      <c r="V31" s="4"/>
       <c r="W31" s="4"/>
-      <c r="X31" s="4" t="s">
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="Y31" s="4" t="s">
+      <c r="Z31" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="Z31" s="4" t="s">
+      <c r="AA31" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA31" s="4" t="s">
+      <c r="AB31" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="AB31" s="5">
+      <c r="AC31" s="5">
         <v>45691</v>
       </c>
-      <c r="AC31" s="12" t="s">
+      <c r="AD31" s="5"/>
+      <c r="AE31" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="AD31" s="12" t="s">
+      <c r="AF31" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AE31" s="4" t="s">
+      <c r="AG31" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF31" s="4" t="s">
+      <c r="AH31" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG31" t="str">
+      <c r="AI31" t="str">
         <f t="shared" si="0"/>
         <v>GTX1_GTX4 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -4252,33 +4372,33 @@
         <v>117</v>
       </c>
       <c r="S32" s="4"/>
-      <c r="T32" s="4" t="s">
+      <c r="U32" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
-      <c r="Z32" s="4" t="s">
+      <c r="X32" s="4"/>
+      <c r="AA32" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AC32" s="12" t="s">
+      <c r="AE32" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="AD32" s="12" t="s">
+      <c r="AF32" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="AE32" s="4" t="s">
+      <c r="AG32" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF32" s="4" t="s">
+      <c r="AH32" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG32" t="str">
+      <c r="AI32" t="str">
         <f t="shared" si="0"/>
         <v>GTX2_3_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -4324,47 +4444,48 @@
       <c r="S33" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T33" s="4" t="s">
+      <c r="U33" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="U33" s="4">
+      <c r="V33" s="4">
         <v>80</v>
       </c>
-      <c r="V33" s="4"/>
       <c r="W33" s="4"/>
-      <c r="X33" s="4" t="s">
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="Y33" s="4" t="s">
+      <c r="Z33" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="Z33" s="4" t="s">
+      <c r="AA33" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA33" s="4" t="s">
+      <c r="AB33" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AB33" s="5">
+      <c r="AC33" s="5">
         <v>45691</v>
       </c>
-      <c r="AC33" s="12" t="s">
+      <c r="AD33" s="5"/>
+      <c r="AE33" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="AD33" s="12" t="s">
+      <c r="AF33" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="AE33" s="4" t="s">
+      <c r="AG33" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF33" s="4" t="s">
+      <c r="AH33" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG33" t="str">
+      <c r="AI33" t="str">
         <f t="shared" si="0"/>
         <v>GTX2_GTX3 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>36</v>
       </c>
@@ -4398,33 +4519,33 @@
         <v>117</v>
       </c>
       <c r="S34" s="4"/>
-      <c r="T34" s="4" t="s">
+      <c r="U34" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
-      <c r="Z34" s="4" t="s">
+      <c r="X34" s="4"/>
+      <c r="AA34" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AC34" s="12" t="s">
+      <c r="AE34" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="AD34" s="12" t="s">
+      <c r="AF34" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="AE34" s="4" t="s">
+      <c r="AG34" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF34" s="4" t="s">
+      <c r="AH34" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG34" t="str">
-        <f t="shared" ref="AG34:AG65" si="1">CONCATENATE(AC34, " (", AE34, ")")</f>
+      <c r="AI34" t="str">
+        <f t="shared" ref="AI34:AI65" si="1">CONCATENATE(AE34, " (", AG34, ")")</f>
         <v>GTX5_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -4460,7 +4581,7 @@
       <c r="O35" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P35" s="22" t="s">
+      <c r="P35" s="21" t="s">
         <v>385</v>
       </c>
       <c r="Q35" s="4" t="s">
@@ -4472,47 +4593,48 @@
       <c r="S35" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T35" s="4" t="s">
+      <c r="U35" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="U35" s="4">
+      <c r="V35" s="4">
         <v>8</v>
       </c>
-      <c r="V35" s="4"/>
       <c r="W35" s="4"/>
-      <c r="X35" s="4" t="s">
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Y35" s="4" t="s">
+      <c r="Z35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="Z35" s="4" t="s">
+      <c r="AA35" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA35" s="20" t="s">
+      <c r="AB35" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="AB35" s="5">
+      <c r="AC35" s="5">
         <v>45691</v>
       </c>
-      <c r="AC35" s="12" t="s">
+      <c r="AD35" s="5"/>
+      <c r="AE35" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AD35" s="12" t="s">
+      <c r="AF35" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="AE35" s="4" t="s">
+      <c r="AG35" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF35" s="4" t="s">
+      <c r="AH35" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG35" t="str">
+      <c r="AI35" t="str">
         <f t="shared" si="1"/>
         <v>GTX5 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>39</v>
       </c>
@@ -4546,33 +4668,33 @@
         <v>117</v>
       </c>
       <c r="S36" s="4"/>
-      <c r="T36" s="4" t="s">
+      <c r="U36" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
-      <c r="Z36" s="4" t="s">
+      <c r="X36" s="4"/>
+      <c r="AA36" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AC36" s="12" t="s">
+      <c r="AE36" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="AD36" s="12" t="s">
+      <c r="AF36" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="AE36" s="4" t="s">
+      <c r="AG36" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF36" s="4" t="s">
+      <c r="AH36" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG36" t="str">
+      <c r="AI36" t="str">
         <f t="shared" si="1"/>
         <v>GTX6_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>38</v>
       </c>
@@ -4608,7 +4730,7 @@
       <c r="O37" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P37" s="22" t="s">
+      <c r="P37" s="21" t="s">
         <v>386</v>
       </c>
       <c r="Q37" s="4" t="s">
@@ -4620,45 +4742,46 @@
       <c r="S37" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T37" s="4" t="s">
+      <c r="U37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
-      <c r="X37" s="4" t="s">
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Y37" s="4" t="s">
+      <c r="Z37" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Z37" s="4" t="s">
+      <c r="AA37" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA37" s="20" t="s">
+      <c r="AB37" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="AB37" s="5">
+      <c r="AC37" s="5">
         <v>45691</v>
       </c>
-      <c r="AC37" s="12" t="s">
+      <c r="AD37" s="5"/>
+      <c r="AE37" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AD37" s="12" t="s">
+      <c r="AF37" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="AE37" s="4" t="s">
+      <c r="AG37" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF37" s="4" t="s">
+      <c r="AH37" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG37" t="str">
+      <c r="AI37" t="str">
         <f t="shared" si="1"/>
         <v>GTX6 (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="38" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>169</v>
       </c>
@@ -4692,7 +4815,6 @@
         <v>117</v>
       </c>
       <c r="S38" s="12"/>
-      <c r="T38" s="12"/>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
@@ -4700,25 +4822,27 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12"/>
       <c r="AA38" s="12"/>
-      <c r="AB38" s="15"/>
-      <c r="AC38" s="12" t="s">
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="5"/>
+      <c r="AD38" s="5"/>
+      <c r="AE38" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="AD38" s="12" t="s">
+      <c r="AF38" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="AE38" s="12" t="s">
+      <c r="AG38" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AF38" s="12" t="s">
+      <c r="AH38" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AG38" s="14" t="str">
+      <c r="AI38" s="14" t="str">
         <f t="shared" si="1"/>
         <v>NEO_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>40</v>
       </c>
@@ -4754,7 +4878,7 @@
       <c r="O39" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P39" s="22" t="s">
+      <c r="P39" s="21" t="s">
         <v>387</v>
       </c>
       <c r="Q39" s="4" t="s">
@@ -4766,47 +4890,48 @@
       <c r="S39" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T39" s="4" t="s">
+      <c r="U39" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="U39" s="4">
+      <c r="V39" s="4">
         <v>167</v>
       </c>
-      <c r="V39" s="4"/>
       <c r="W39" s="4"/>
-      <c r="X39" s="4" t="s">
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="Y39" s="4" t="s">
+      <c r="Z39" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="Z39" s="4" t="s">
+      <c r="AA39" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA39" s="20" t="s">
+      <c r="AB39" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="AB39" s="5">
+      <c r="AC39" s="5">
         <v>45691</v>
       </c>
-      <c r="AC39" s="12" t="s">
+      <c r="AD39" s="5"/>
+      <c r="AE39" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="AD39" s="12" t="s">
+      <c r="AF39" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="AE39" s="4" t="s">
+      <c r="AG39" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF39" s="4" t="s">
+      <c r="AH39" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG39" t="str">
+      <c r="AI39" t="str">
         <f t="shared" si="1"/>
         <v>NeoSTX (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="40" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>170</v>
       </c>
@@ -4840,7 +4965,6 @@
         <v>117</v>
       </c>
       <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
       <c r="U40" s="12"/>
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
@@ -4848,25 +4972,27 @@
       <c r="Y40" s="12"/>
       <c r="Z40" s="12"/>
       <c r="AA40" s="12"/>
-      <c r="AB40" s="15"/>
-      <c r="AC40" s="12" t="s">
+      <c r="AB40" s="4"/>
+      <c r="AC40" s="5"/>
+      <c r="AD40" s="5"/>
+      <c r="AE40" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="AD40" s="12" t="s">
+      <c r="AF40" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="AE40" s="12" t="s">
+      <c r="AG40" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AF40" s="12" t="s">
+      <c r="AH40" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="AG40" s="14" t="str">
+      <c r="AI40" s="14" t="str">
         <f t="shared" si="1"/>
         <v>PST_tot_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="41" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>41</v>
       </c>
@@ -4909,44 +5035,45 @@
       <c r="R41" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="S41" s="16" t="s">
+      <c r="S41" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="T41" s="12" t="s">
+      <c r="U41" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="U41" s="12">
+      <c r="V41" s="12">
         <v>380</v>
       </c>
-      <c r="V41" s="12">
+      <c r="W41" s="12">
         <v>800</v>
       </c>
-      <c r="W41" s="12"/>
       <c r="X41" s="12"/>
       <c r="Y41" s="12"/>
-      <c r="Z41" s="12" t="s">
+      <c r="Z41" s="12"/>
+      <c r="AA41" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="AA41" s="12"/>
-      <c r="AB41" s="15"/>
-      <c r="AC41" s="12" t="s">
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="5"/>
+      <c r="AD41" s="5"/>
+      <c r="AE41" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="AD41" s="12" t="s">
+      <c r="AF41" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="AE41" s="12" t="s">
+      <c r="AG41" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="AF41" s="12" t="s">
+      <c r="AH41" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="AG41" s="14" t="str">
+      <c r="AI41" s="14" t="str">
         <f t="shared" si="1"/>
         <v>PST_tot (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -4970,37 +5097,37 @@
       <c r="M42" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="P42" s="21"/>
+      <c r="P42" s="20"/>
       <c r="Q42" s="4" t="s">
         <v>117</v>
       </c>
       <c r="R42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="T42" s="4" t="s">
+      <c r="U42" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="Z42" s="4" t="s">
+      <c r="AA42" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AC42" s="12" t="s">
+      <c r="AE42" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="AD42" s="12" t="s">
+      <c r="AF42" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="AE42" s="4" t="s">
+      <c r="AG42" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AF42" s="4" t="s">
+      <c r="AH42" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AG42" t="str">
+      <c r="AI42" t="str">
         <f t="shared" si="1"/>
         <v>STX_screen_pos (true or false)</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>43</v>
       </c>
@@ -5036,7 +5163,7 @@
       <c r="O43" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P43" s="22" t="s">
+      <c r="P43" s="21" t="s">
         <v>381</v>
       </c>
       <c r="Q43" s="4" t="s">
@@ -5048,49 +5175,50 @@
       <c r="S43" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="T43" s="4" t="s">
+      <c r="U43" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="U43" s="4">
+      <c r="V43" s="4">
         <v>40</v>
       </c>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4">
+      <c r="W43" s="4"/>
+      <c r="X43" s="4">
         <v>1</v>
       </c>
-      <c r="X43" s="4" t="s">
+      <c r="Y43" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Y43" s="4" t="s">
+      <c r="Z43" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="Z43" s="4" t="s">
+      <c r="AA43" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA43" s="20" t="s">
+      <c r="AB43" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="AB43" s="5">
+      <c r="AC43" s="5">
         <v>45691</v>
       </c>
-      <c r="AC43" s="12" t="s">
+      <c r="AD43" s="5"/>
+      <c r="AE43" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AD43" s="12" t="s">
+      <c r="AF43" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="AE43" s="4" t="s">
+      <c r="AG43" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AF43" s="4" t="s">
+      <c r="AH43" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AG43" t="str">
+      <c r="AI43" t="str">
         <f t="shared" si="1"/>
         <v>STX (ug STXdiHCL eq/kg)</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>22</v>
       </c>
@@ -5136,39 +5264,40 @@
       <c r="S44" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="T44" s="4" t="s">
+      <c r="U44" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="U44" s="4"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
-      <c r="Z44" s="4" t="s">
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="5">
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="5">
         <v>45691</v>
       </c>
-      <c r="AC44" s="12" t="s">
+      <c r="AD44" s="5"/>
+      <c r="AE44" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD44" s="12" t="s">
+      <c r="AF44" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AE44" s="4" t="s">
+      <c r="AG44" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="AF44" s="4" t="s">
+      <c r="AH44" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="AG44" t="str">
+      <c r="AI44" t="str">
         <f t="shared" si="1"/>
         <v>SPX1 (ug/kg)</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>2</v>
       </c>
@@ -5214,47 +5343,48 @@
       <c r="S45" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T45" s="4" t="s">
+      <c r="U45" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="U45" s="4">
+      <c r="V45" s="4">
         <v>0.1</v>
       </c>
-      <c r="V45" s="4"/>
       <c r="W45" s="4"/>
-      <c r="X45" s="4" t="s">
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y45" s="4" t="s">
+      <c r="Z45" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Z45" s="4" t="s">
+      <c r="AA45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA45" s="20" t="s">
+      <c r="AB45" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="AB45" s="5">
+      <c r="AC45" s="5">
         <v>45691</v>
       </c>
-      <c r="AC45" s="12" t="s">
+      <c r="AD45" s="5"/>
+      <c r="AE45" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="AD45" s="12" t="s">
+      <c r="AF45" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AE45" s="4" t="s">
+      <c r="AG45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF45" s="4" t="s">
+      <c r="AH45" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG45" t="str">
+      <c r="AI45" t="str">
         <f t="shared" si="1"/>
         <v>45OH_carboxyYTX (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>3</v>
       </c>
@@ -5290,7 +5420,7 @@
       <c r="O46" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P46" s="22" t="s">
+      <c r="P46" s="21" t="s">
         <v>388</v>
       </c>
       <c r="Q46" s="4" t="s">
@@ -5302,47 +5432,50 @@
       <c r="S46" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T46" s="4" t="s">
+      <c r="U46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="U46" s="4">
+      <c r="V46" s="4">
         <v>0.1</v>
       </c>
-      <c r="V46" s="4"/>
       <c r="W46" s="4"/>
-      <c r="X46" s="4" t="s">
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y46" s="4" t="s">
+      <c r="Z46" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Z46" s="4" t="s">
+      <c r="AA46" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA46" s="20" t="s">
+      <c r="AB46" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="AB46" s="5">
+      <c r="AC46" s="5">
         <v>45691</v>
       </c>
-      <c r="AC46" s="12" t="s">
+      <c r="AD46" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="AE46" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="AD46" s="12" t="s">
+      <c r="AF46" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="AE46" s="4" t="s">
+      <c r="AG46" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF46" s="4" t="s">
+      <c r="AH46" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG46" t="str">
+      <c r="AI46" t="str">
         <f t="shared" si="1"/>
         <v>45_OH_homoYTX (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>4</v>
       </c>
@@ -5378,7 +5511,7 @@
       <c r="O47" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P47" s="22" t="s">
+      <c r="P47" s="21" t="s">
         <v>389</v>
       </c>
       <c r="Q47" s="4" t="s">
@@ -5390,47 +5523,50 @@
       <c r="S47" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T47" s="4" t="s">
+      <c r="U47" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="U47" s="4">
+      <c r="V47" s="4">
         <v>0.1</v>
       </c>
-      <c r="V47" s="4"/>
       <c r="W47" s="4"/>
-      <c r="X47" s="4" t="s">
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="Y47" s="4" t="s">
+      <c r="Z47" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Z47" s="4" t="s">
+      <c r="AA47" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA47" s="20" t="s">
+      <c r="AB47" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AB47" s="5">
+      <c r="AC47" s="5">
         <v>45691</v>
       </c>
-      <c r="AC47" s="12" t="s">
+      <c r="AD47" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="AE47" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="AD47" s="12" t="s">
+      <c r="AF47" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="AE47" s="4" t="s">
+      <c r="AG47" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF47" s="4" t="s">
+      <c r="AH47" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG47" t="str">
+      <c r="AI47" t="str">
         <f t="shared" si="1"/>
         <v>45_OH_YTX (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
@@ -5466,7 +5602,7 @@
       <c r="O48" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P48" s="22" t="s">
+      <c r="P48" s="21" t="s">
         <v>390</v>
       </c>
       <c r="Q48" s="4" t="s">
@@ -5478,47 +5614,50 @@
       <c r="S48" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T48" s="4" t="s">
+      <c r="U48" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="U48" s="4">
+      <c r="V48" s="4">
         <v>0.1</v>
       </c>
-      <c r="V48" s="4"/>
       <c r="W48" s="4"/>
-      <c r="X48" s="4" t="s">
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y48" s="4" t="s">
+      <c r="Z48" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Z48" s="4" t="s">
+      <c r="AA48" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA48" s="20" t="s">
+      <c r="AB48" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="AB48" s="5">
+      <c r="AC48" s="5">
         <v>45691</v>
       </c>
-      <c r="AC48" s="12" t="s">
+      <c r="AD48" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="AE48" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="AD48" s="12" t="s">
+      <c r="AF48" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="AE48" s="4" t="s">
+      <c r="AG48" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF48" s="4" t="s">
+      <c r="AH48" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG48" t="str">
+      <c r="AI48" t="str">
         <f t="shared" si="1"/>
         <v>CarboxyYTX (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>16</v>
       </c>
@@ -5554,7 +5693,7 @@
       <c r="O49" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P49" s="22" t="s">
+      <c r="P49" s="21" t="s">
         <v>391</v>
       </c>
       <c r="Q49" s="4" t="s">
@@ -5566,47 +5705,50 @@
       <c r="S49" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T49" s="4" t="s">
+      <c r="U49" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="U49" s="4">
+      <c r="V49" s="4">
         <v>0.1</v>
       </c>
-      <c r="V49" s="4"/>
       <c r="W49" s="4"/>
-      <c r="X49" s="4" t="s">
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="Y49" s="4" t="s">
+      <c r="Z49" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="Z49" s="4" t="s">
+      <c r="AA49" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA49" s="20" t="s">
+      <c r="AB49" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AB49" s="5">
+      <c r="AC49" s="5">
         <v>45691</v>
       </c>
-      <c r="AC49" s="12" t="s">
+      <c r="AD49" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="AE49" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AD49" s="12" t="s">
+      <c r="AF49" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="AE49" s="4" t="s">
+      <c r="AG49" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF49" s="4" t="s">
+      <c r="AH49" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG49" t="str">
+      <c r="AI49" t="str">
         <f t="shared" si="1"/>
         <v>HomoYTX (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>23</v>
       </c>
@@ -5642,7 +5784,7 @@
       <c r="O50" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P50" s="22" t="s">
+      <c r="P50" s="21" t="s">
         <v>392</v>
       </c>
       <c r="Q50" s="4" t="s">
@@ -5654,49 +5796,52 @@
       <c r="S50" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T50" s="4" t="s">
+      <c r="U50" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="U50" s="4">
+      <c r="V50" s="4">
         <v>0.1</v>
       </c>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4">
+      <c r="W50" s="4"/>
+      <c r="X50" s="4">
         <v>1</v>
       </c>
-      <c r="X50" s="4" t="s">
+      <c r="Y50" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="Y50" s="4" t="s">
+      <c r="Z50" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="Z50" s="4" t="s">
+      <c r="AA50" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA50" s="20" t="s">
+      <c r="AB50" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AB50" s="5">
+      <c r="AC50" s="5">
         <v>45691</v>
       </c>
-      <c r="AC50" s="12" t="s">
+      <c r="AD50" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE50" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="AD50" s="12" t="s">
+      <c r="AF50" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="AE50" s="4" t="s">
+      <c r="AG50" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF50" s="4" t="s">
+      <c r="AH50" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG50" t="str">
+      <c r="AI50" t="str">
         <f t="shared" si="1"/>
         <v>YTX (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>24</v>
       </c>
@@ -5742,43 +5887,46 @@
       <c r="S51" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T51" s="4" t="s">
+      <c r="U51" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="U51" s="4">
+      <c r="V51" s="4">
         <v>0.1</v>
       </c>
-      <c r="V51" s="4">
+      <c r="W51" s="4">
         <v>3.75</v>
       </c>
-      <c r="W51" s="4"/>
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
-      <c r="Z51" s="4" t="s">
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="5" t="s">
+      <c r="AB51" s="4"/>
+      <c r="AC51" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AC51" s="12" t="s">
+      <c r="AD51" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE51" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="AD51" s="12" t="s">
+      <c r="AF51" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="AE51" s="4" t="s">
+      <c r="AG51" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AF51" s="4" t="s">
+      <c r="AH51" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AG51" t="str">
+      <c r="AI51" t="str">
         <f t="shared" si="1"/>
         <v>YTX_tot (mg YTX eq/kg)</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -5795,34 +5943,34 @@
       <c r="N52" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="P52" s="21"/>
+      <c r="P52" s="20"/>
       <c r="Q52" s="4" t="s">
         <v>337</v>
       </c>
       <c r="R52" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="Z52" t="s">
+      <c r="AA52" t="s">
         <v>48</v>
       </c>
-      <c r="AC52" s="12" t="s">
+      <c r="AE52" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="AD52" s="12" t="s">
+      <c r="AF52" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="AE52" t="s">
+      <c r="AG52" t="s">
         <v>48</v>
       </c>
-      <c r="AF52" t="s">
+      <c r="AH52" t="s">
         <v>329</v>
       </c>
-      <c r="AG52" t="str">
+      <c r="AI52" t="str">
         <f t="shared" si="1"/>
         <v>Ana_a (mg/kg)</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -5838,34 +5986,34 @@
       <c r="N53" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="P53" s="21"/>
+      <c r="P53" s="20"/>
       <c r="Q53" s="4" t="s">
         <v>337</v>
       </c>
       <c r="R53" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="Z53" t="s">
+      <c r="AA53" t="s">
         <v>48</v>
       </c>
-      <c r="AC53" s="12" t="s">
+      <c r="AE53" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="AD53" s="12" t="s">
+      <c r="AF53" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="AE53" t="s">
+      <c r="AG53" t="s">
         <v>48</v>
       </c>
-      <c r="AF53" t="s">
+      <c r="AH53" t="s">
         <v>329</v>
       </c>
-      <c r="AG53" t="str">
+      <c r="AI53" t="str">
         <f t="shared" si="1"/>
         <v>h_Ana (mg/kg)</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>244</v>
       </c>
@@ -5884,7 +6032,7 @@
       <c r="O54" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="P54" s="22" t="s">
+      <c r="P54" s="21" t="s">
         <v>393</v>
       </c>
       <c r="Q54" s="4" t="s">
@@ -5896,42 +6044,43 @@
       <c r="S54" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="T54" s="4" t="s">
+      <c r="U54" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="X54" s="4" t="s">
+      <c r="Y54" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="Y54" s="4" t="s">
+      <c r="Z54" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="Z54" t="s">
+      <c r="AA54" t="s">
         <v>48</v>
       </c>
-      <c r="AA54" s="20" t="s">
+      <c r="AB54" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="AB54" s="5">
+      <c r="AC54" s="5">
         <v>45698</v>
       </c>
-      <c r="AC54" s="12" t="s">
+      <c r="AD54" s="5"/>
+      <c r="AE54" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="AD54" s="12" t="s">
+      <c r="AF54" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="AE54" t="s">
+      <c r="AG54" t="s">
         <v>48</v>
       </c>
-      <c r="AF54" t="s">
+      <c r="AH54" t="s">
         <v>329</v>
       </c>
-      <c r="AG54" t="str">
+      <c r="AI54" t="str">
         <f t="shared" si="1"/>
         <v>CYN (mg/kg)</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>235</v>
       </c>
@@ -5950,7 +6099,7 @@
       <c r="O55" t="s">
         <v>249</v>
       </c>
-      <c r="P55" s="21"/>
+      <c r="P55" s="20"/>
       <c r="Q55" s="4" t="s">
         <v>337</v>
       </c>
@@ -5960,42 +6109,43 @@
       <c r="S55" t="s">
         <v>248</v>
       </c>
-      <c r="T55" t="s">
+      <c r="U55" t="s">
         <v>235</v>
       </c>
-      <c r="X55" t="s">
+      <c r="Y55" t="s">
         <v>231</v>
       </c>
-      <c r="Y55" t="s">
+      <c r="Z55" t="s">
         <v>257</v>
       </c>
-      <c r="Z55" t="s">
+      <c r="AA55" t="s">
         <v>48</v>
       </c>
-      <c r="AA55" s="20" t="s">
+      <c r="AB55" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="AB55" s="5">
+      <c r="AC55" s="5">
         <v>45698</v>
       </c>
-      <c r="AC55" s="12" t="s">
+      <c r="AD55" s="5"/>
+      <c r="AE55" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="AD55" s="12" t="s">
+      <c r="AF55" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="AE55" t="s">
+      <c r="AG55" t="s">
         <v>48</v>
       </c>
-      <c r="AF55" t="s">
+      <c r="AH55" t="s">
         <v>329</v>
       </c>
-      <c r="AG55" t="str">
+      <c r="AI55" t="str">
         <f t="shared" si="1"/>
         <v>MC_HilR (mg/kg)</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>239</v>
       </c>
@@ -6014,7 +6164,7 @@
       <c r="O56" t="s">
         <v>249</v>
       </c>
-      <c r="P56" s="21"/>
+      <c r="P56" s="20"/>
       <c r="Q56" s="4" t="s">
         <v>337</v>
       </c>
@@ -6024,27 +6174,27 @@
       <c r="S56" t="s">
         <v>248</v>
       </c>
-      <c r="Z56" t="s">
+      <c r="AA56" t="s">
         <v>48</v>
       </c>
-      <c r="AC56" s="12" t="s">
+      <c r="AE56" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="AD56" s="12" t="s">
+      <c r="AF56" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="AE56" t="s">
+      <c r="AG56" t="s">
         <v>48</v>
       </c>
-      <c r="AF56" t="s">
+      <c r="AH56" t="s">
         <v>329</v>
       </c>
-      <c r="AG56" t="str">
+      <c r="AI56" t="str">
         <f t="shared" si="1"/>
         <v>MC_HphR_DAsp3_E_Dhb7 (mg/kg)</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>223</v>
       </c>
@@ -6063,7 +6213,7 @@
       <c r="O57" t="s">
         <v>249</v>
       </c>
-      <c r="P57" s="21"/>
+      <c r="P57" s="20"/>
       <c r="Q57" s="4" t="s">
         <v>337</v>
       </c>
@@ -6073,42 +6223,43 @@
       <c r="S57" t="s">
         <v>248</v>
       </c>
-      <c r="T57" s="4" t="s">
+      <c r="U57" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="X57" s="4" t="s">
+      <c r="Y57" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="Y57" s="4" t="s">
+      <c r="Z57" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="Z57" t="s">
+      <c r="AA57" t="s">
         <v>48</v>
       </c>
-      <c r="AA57" s="20" t="s">
+      <c r="AB57" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="AB57" s="5">
+      <c r="AC57" s="5">
         <v>45700</v>
       </c>
-      <c r="AC57" s="12" t="s">
+      <c r="AD57" s="5"/>
+      <c r="AE57" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="AD57" s="12" t="s">
+      <c r="AF57" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="AE57" t="s">
+      <c r="AG57" t="s">
         <v>48</v>
       </c>
-      <c r="AF57" t="s">
+      <c r="AH57" t="s">
         <v>329</v>
       </c>
-      <c r="AG57" t="str">
+      <c r="AI57" t="str">
         <f t="shared" si="1"/>
         <v>MC_HTyR (mg/kg)</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>240</v>
       </c>
@@ -6127,7 +6278,7 @@
       <c r="O58" t="s">
         <v>249</v>
       </c>
-      <c r="P58" s="21"/>
+      <c r="P58" s="20"/>
       <c r="Q58" s="4" t="s">
         <v>337</v>
       </c>
@@ -6137,27 +6288,27 @@
       <c r="S58" t="s">
         <v>248</v>
       </c>
-      <c r="Z58" t="s">
+      <c r="AA58" t="s">
         <v>48</v>
       </c>
-      <c r="AC58" s="12" t="s">
+      <c r="AE58" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="AD58" s="12" t="s">
+      <c r="AF58" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="AE58" t="s">
+      <c r="AG58" t="s">
         <v>48</v>
       </c>
-      <c r="AF58" t="s">
+      <c r="AH58" t="s">
         <v>329</v>
       </c>
-      <c r="AG58" t="str">
+      <c r="AI58" t="str">
         <f t="shared" si="1"/>
         <v>MC_HtyR_D_Asp3_E_Dhb7 (mg/kg)</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>230</v>
       </c>
@@ -6176,7 +6327,7 @@
       <c r="O59" t="s">
         <v>249</v>
       </c>
-      <c r="P59" s="21"/>
+      <c r="P59" s="20"/>
       <c r="Q59" s="4" t="s">
         <v>337</v>
       </c>
@@ -6186,42 +6337,45 @@
       <c r="S59" t="s">
         <v>248</v>
       </c>
-      <c r="T59" t="s">
+      <c r="U59" t="s">
         <v>230</v>
       </c>
-      <c r="X59" t="s">
+      <c r="Y59" t="s">
         <v>230</v>
       </c>
-      <c r="Y59" t="s">
+      <c r="Z59" t="s">
         <v>251</v>
       </c>
-      <c r="Z59" t="s">
+      <c r="AA59" t="s">
         <v>48</v>
       </c>
-      <c r="AA59" s="20" t="s">
+      <c r="AB59" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="AB59" s="5">
+      <c r="AC59" s="5">
         <v>45698</v>
       </c>
-      <c r="AC59" s="12" t="s">
+      <c r="AD59" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="AE59" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="AD59" s="12" t="s">
+      <c r="AF59" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="AE59" t="s">
+      <c r="AG59" t="s">
         <v>48</v>
       </c>
-      <c r="AF59" t="s">
+      <c r="AH59" t="s">
         <v>329</v>
       </c>
-      <c r="AG59" t="str">
+      <c r="AI59" t="str">
         <f t="shared" si="1"/>
         <v>MC_LA (mg/kg)</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>231</v>
       </c>
@@ -6240,7 +6394,7 @@
       <c r="O60" t="s">
         <v>249</v>
       </c>
-      <c r="P60" s="21"/>
+      <c r="P60" s="20"/>
       <c r="Q60" s="4" t="s">
         <v>337</v>
       </c>
@@ -6250,42 +6404,45 @@
       <c r="S60" t="s">
         <v>248</v>
       </c>
-      <c r="T60" t="s">
+      <c r="U60" t="s">
         <v>231</v>
       </c>
-      <c r="X60" t="s">
+      <c r="Y60" t="s">
         <v>231</v>
       </c>
-      <c r="Y60" t="s">
+      <c r="Z60" t="s">
         <v>253</v>
       </c>
-      <c r="Z60" t="s">
+      <c r="AA60" t="s">
         <v>48</v>
       </c>
-      <c r="AA60" s="20" t="s">
+      <c r="AB60" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="AB60" s="5">
+      <c r="AC60" s="5">
         <v>45698</v>
       </c>
-      <c r="AC60" s="12" t="s">
+      <c r="AD60" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="AE60" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="AD60" s="12" t="s">
+      <c r="AF60" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="AE60" t="s">
+      <c r="AG60" t="s">
         <v>48</v>
       </c>
-      <c r="AF60" t="s">
+      <c r="AH60" t="s">
         <v>329</v>
       </c>
-      <c r="AG60" t="str">
+      <c r="AI60" t="str">
         <f t="shared" si="1"/>
         <v>MC_LF (mg/kg)</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>228</v>
       </c>
@@ -6304,7 +6461,7 @@
       <c r="O61" t="s">
         <v>249</v>
       </c>
-      <c r="P61" s="21"/>
+      <c r="P61" s="20"/>
       <c r="Q61" s="4" t="s">
         <v>337</v>
       </c>
@@ -6314,42 +6471,45 @@
       <c r="S61" t="s">
         <v>248</v>
       </c>
-      <c r="T61" t="s">
+      <c r="U61" t="s">
         <v>228</v>
       </c>
-      <c r="X61" t="s">
+      <c r="Y61" t="s">
         <v>228</v>
       </c>
-      <c r="Y61" t="s">
+      <c r="Z61" t="s">
         <v>246</v>
       </c>
-      <c r="Z61" t="s">
+      <c r="AA61" t="s">
         <v>48</v>
       </c>
-      <c r="AA61" s="20" t="s">
+      <c r="AB61" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="AB61" s="5">
+      <c r="AC61" s="5">
         <v>45698</v>
       </c>
-      <c r="AC61" s="12" t="s">
+      <c r="AD61" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="AE61" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="AD61" s="12" t="s">
+      <c r="AF61" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="AE61" t="s">
+      <c r="AG61" t="s">
         <v>48</v>
       </c>
-      <c r="AF61" t="s">
+      <c r="AH61" t="s">
         <v>329</v>
       </c>
-      <c r="AG61" t="str">
+      <c r="AI61" t="str">
         <f t="shared" si="1"/>
         <v>MC_LR (mg/kg)</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>224</v>
       </c>
@@ -6376,7 +6536,7 @@
       <c r="O62" t="s">
         <v>249</v>
       </c>
-      <c r="P62" s="21"/>
+      <c r="P62" s="20"/>
       <c r="Q62" s="4" t="s">
         <v>337</v>
       </c>
@@ -6386,42 +6546,43 @@
       <c r="S62" t="s">
         <v>248</v>
       </c>
-      <c r="T62" t="s">
+      <c r="U62" t="s">
         <v>309</v>
       </c>
-      <c r="X62" t="s">
+      <c r="Y62" t="s">
         <v>309</v>
       </c>
-      <c r="Y62" t="s">
+      <c r="Z62" t="s">
         <v>310</v>
       </c>
-      <c r="Z62" t="s">
+      <c r="AA62" t="s">
         <v>48</v>
       </c>
-      <c r="AA62" s="20" t="s">
+      <c r="AB62" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="AB62" s="5">
+      <c r="AC62" s="5">
         <v>45700</v>
       </c>
-      <c r="AC62" s="12" t="s">
+      <c r="AD62" s="5"/>
+      <c r="AE62" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="AD62" s="12" t="s">
+      <c r="AF62" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="AE62" t="s">
+      <c r="AG62" t="s">
         <v>48</v>
       </c>
-      <c r="AF62" t="s">
+      <c r="AH62" t="s">
         <v>329</v>
       </c>
-      <c r="AG62" t="str">
+      <c r="AI62" t="str">
         <f t="shared" si="1"/>
         <v>MC_LR_D_Asp3 (mg/kg)</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>237</v>
       </c>
@@ -6448,7 +6609,7 @@
       <c r="O63" t="s">
         <v>249</v>
       </c>
-      <c r="P63" s="21"/>
+      <c r="P63" s="20"/>
       <c r="Q63" s="4" t="s">
         <v>337</v>
       </c>
@@ -6458,42 +6619,43 @@
       <c r="S63" t="s">
         <v>248</v>
       </c>
-      <c r="T63" t="s">
+      <c r="U63" t="s">
         <v>320</v>
       </c>
-      <c r="X63" t="s">
+      <c r="Y63" t="s">
         <v>320</v>
       </c>
-      <c r="Y63" t="s">
+      <c r="Z63" t="s">
         <v>319</v>
       </c>
-      <c r="Z63" t="s">
+      <c r="AA63" t="s">
         <v>48</v>
       </c>
-      <c r="AA63" t="s">
+      <c r="AB63" t="s">
         <v>318</v>
       </c>
-      <c r="AB63" s="5">
+      <c r="AC63" s="5">
         <v>45700</v>
       </c>
-      <c r="AC63" s="12" t="s">
+      <c r="AD63" s="5"/>
+      <c r="AE63" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="AD63" s="12" t="s">
+      <c r="AF63" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="AE63" t="s">
+      <c r="AG63" t="s">
         <v>48</v>
       </c>
-      <c r="AF63" t="s">
+      <c r="AH63" t="s">
         <v>329</v>
       </c>
-      <c r="AG63" t="str">
+      <c r="AI63" t="str">
         <f t="shared" si="1"/>
         <v>MC_LR_Dha7 (mg/kg)</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>232</v>
       </c>
@@ -6512,7 +6674,7 @@
       <c r="O64" t="s">
         <v>249</v>
       </c>
-      <c r="P64" s="21"/>
+      <c r="P64" s="20"/>
       <c r="Q64" s="4" t="s">
         <v>337</v>
       </c>
@@ -6522,42 +6684,45 @@
       <c r="S64" t="s">
         <v>248</v>
       </c>
-      <c r="T64" t="s">
+      <c r="U64" t="s">
         <v>232</v>
       </c>
-      <c r="X64" t="s">
+      <c r="Y64" t="s">
         <v>231</v>
       </c>
-      <c r="Y64" t="s">
+      <c r="Z64" t="s">
         <v>254</v>
       </c>
-      <c r="Z64" t="s">
+      <c r="AA64" t="s">
         <v>48</v>
       </c>
-      <c r="AA64" t="s">
+      <c r="AB64" t="s">
         <v>258</v>
       </c>
-      <c r="AB64" s="5">
+      <c r="AC64" s="5">
         <v>45698</v>
       </c>
-      <c r="AC64" s="12" t="s">
+      <c r="AD64" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="AE64" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="AD64" s="12" t="s">
+      <c r="AF64" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="AE64" t="s">
+      <c r="AG64" t="s">
         <v>48</v>
       </c>
-      <c r="AF64" t="s">
+      <c r="AH64" t="s">
         <v>329</v>
       </c>
-      <c r="AG64" t="str">
+      <c r="AI64" t="str">
         <f t="shared" si="1"/>
         <v>MC_LW (mg/kg)</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>233</v>
       </c>
@@ -6576,7 +6741,7 @@
       <c r="O65" t="s">
         <v>249</v>
       </c>
-      <c r="P65" s="21"/>
+      <c r="P65" s="20"/>
       <c r="Q65" s="4" t="s">
         <v>337</v>
       </c>
@@ -6586,42 +6751,45 @@
       <c r="S65" t="s">
         <v>248</v>
       </c>
-      <c r="T65" t="s">
+      <c r="U65" t="s">
         <v>233</v>
       </c>
-      <c r="X65" t="s">
+      <c r="Y65" t="s">
         <v>231</v>
       </c>
-      <c r="Y65" t="s">
+      <c r="Z65" t="s">
         <v>255</v>
       </c>
-      <c r="Z65" t="s">
+      <c r="AA65" t="s">
         <v>48</v>
       </c>
-      <c r="AA65" t="s">
+      <c r="AB65" t="s">
         <v>259</v>
       </c>
-      <c r="AB65" s="5">
+      <c r="AC65" s="5">
         <v>45698</v>
       </c>
-      <c r="AC65" s="12" t="s">
+      <c r="AD65" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="AE65" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="AD65" s="12" t="s">
+      <c r="AF65" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="AE65" t="s">
+      <c r="AG65" t="s">
         <v>48</v>
       </c>
-      <c r="AF65" t="s">
+      <c r="AH65" t="s">
         <v>329</v>
       </c>
-      <c r="AG65" t="str">
+      <c r="AI65" t="str">
         <f t="shared" si="1"/>
         <v>MC_LY (mg/kg)</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>227</v>
       </c>
@@ -6640,7 +6808,7 @@
       <c r="O66" t="s">
         <v>249</v>
       </c>
-      <c r="P66" s="21"/>
+      <c r="P66" s="20"/>
       <c r="Q66" s="4" t="s">
         <v>337</v>
       </c>
@@ -6650,45 +6818,48 @@
       <c r="S66" t="s">
         <v>248</v>
       </c>
-      <c r="T66" s="3" t="s">
+      <c r="U66" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="U66" s="3"/>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
-      <c r="X66" s="3" t="s">
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="Y66" s="3" t="s">
+      <c r="Z66" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="Z66" s="3" t="s">
+      <c r="AA66" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AA66" s="3" t="s">
+      <c r="AB66" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="AB66" s="5">
+      <c r="AC66" s="5">
         <v>45698</v>
       </c>
-      <c r="AC66" s="12" t="s">
+      <c r="AD66" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="AE66" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="AD66" s="12" t="s">
+      <c r="AF66" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="AE66" s="3" t="s">
+      <c r="AG66" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AF66" s="3" t="s">
+      <c r="AH66" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="AG66" t="str">
-        <f t="shared" ref="AG66:AG72" si="2">CONCATENATE(AC66, " (", AE66, ")")</f>
+      <c r="AI66" t="str">
+        <f t="shared" ref="AI66:AI72" si="2">CONCATENATE(AE66, " (", AG66, ")")</f>
         <v>MC_RR (mg/kg)</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>236</v>
       </c>
@@ -6715,7 +6886,7 @@
       <c r="O67" t="s">
         <v>249</v>
       </c>
-      <c r="P67" s="21"/>
+      <c r="P67" s="20"/>
       <c r="Q67" s="4" t="s">
         <v>337</v>
       </c>
@@ -6725,27 +6896,27 @@
       <c r="S67" t="s">
         <v>248</v>
       </c>
-      <c r="Z67" t="s">
+      <c r="AA67" t="s">
         <v>48</v>
       </c>
-      <c r="AC67" s="12" t="s">
+      <c r="AE67" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="AD67" s="12" t="s">
+      <c r="AF67" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="AE67" t="s">
+      <c r="AG67" t="s">
         <v>48</v>
       </c>
-      <c r="AF67" t="s">
+      <c r="AH67" t="s">
         <v>329</v>
       </c>
-      <c r="AG67" t="str">
+      <c r="AI67" t="str">
         <f t="shared" si="2"/>
         <v>MC_RR_D_Asp3_E_Dhb7 (mg/kg)</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>225</v>
       </c>
@@ -6772,7 +6943,7 @@
       <c r="O68" t="s">
         <v>249</v>
       </c>
-      <c r="P68" s="21"/>
+      <c r="P68" s="20"/>
       <c r="Q68" s="4" t="s">
         <v>337</v>
       </c>
@@ -6782,42 +6953,43 @@
       <c r="S68" t="s">
         <v>248</v>
       </c>
-      <c r="T68" t="s">
+      <c r="U68" t="s">
         <v>314</v>
       </c>
-      <c r="X68" t="s">
+      <c r="Y68" t="s">
         <v>314</v>
       </c>
-      <c r="Y68" t="s">
+      <c r="Z68" t="s">
         <v>313</v>
       </c>
-      <c r="Z68" t="s">
+      <c r="AA68" t="s">
         <v>48</v>
       </c>
-      <c r="AA68" t="s">
+      <c r="AB68" s="19" t="s">
         <v>312</v>
       </c>
-      <c r="AB68" s="5">
+      <c r="AC68" s="5">
         <v>45700</v>
       </c>
-      <c r="AC68" s="12" t="s">
+      <c r="AD68" s="5"/>
+      <c r="AE68" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="AD68" s="12" t="s">
+      <c r="AF68" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="AE68" t="s">
+      <c r="AG68" t="s">
         <v>48</v>
       </c>
-      <c r="AF68" t="s">
+      <c r="AH68" t="s">
         <v>329</v>
       </c>
-      <c r="AG68" t="str">
+      <c r="AI68" t="str">
         <f t="shared" si="2"/>
         <v>MC_RR_D_Asp3 (mg/kg)</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -6836,7 +7008,7 @@
       <c r="O69" t="s">
         <v>249</v>
       </c>
-      <c r="P69" s="21"/>
+      <c r="P69" s="20"/>
       <c r="Q69" s="4" t="s">
         <v>337</v>
       </c>
@@ -6846,42 +7018,43 @@
       <c r="S69" t="s">
         <v>248</v>
       </c>
-      <c r="T69" t="s">
+      <c r="U69" t="s">
         <v>323</v>
       </c>
-      <c r="X69" t="s">
+      <c r="Y69" t="s">
         <v>323</v>
       </c>
-      <c r="Y69" t="s">
+      <c r="Z69" t="s">
         <v>322</v>
       </c>
-      <c r="Z69" t="s">
+      <c r="AA69" t="s">
         <v>48</v>
       </c>
-      <c r="AA69" t="s">
+      <c r="AB69" t="s">
         <v>321</v>
       </c>
-      <c r="AB69" s="5">
+      <c r="AC69" s="5">
         <v>45700</v>
       </c>
-      <c r="AC69" s="12" t="s">
+      <c r="AD69" s="5"/>
+      <c r="AE69" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="AD69" s="12" t="s">
+      <c r="AF69" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="AE69" t="s">
+      <c r="AG69" t="s">
         <v>48</v>
       </c>
-      <c r="AF69" t="s">
+      <c r="AH69" t="s">
         <v>329</v>
       </c>
-      <c r="AG69" t="str">
+      <c r="AI69" t="str">
         <f t="shared" si="2"/>
         <v>MC_RR_Dha7 (mg/kg)</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>234</v>
       </c>
@@ -6900,7 +7073,7 @@
       <c r="O70" t="s">
         <v>249</v>
       </c>
-      <c r="P70" s="21"/>
+      <c r="P70" s="20"/>
       <c r="Q70" s="4" t="s">
         <v>337</v>
       </c>
@@ -6910,42 +7083,43 @@
       <c r="S70" t="s">
         <v>248</v>
       </c>
-      <c r="T70" t="s">
+      <c r="U70" t="s">
         <v>234</v>
       </c>
-      <c r="X70" t="s">
+      <c r="Y70" t="s">
         <v>231</v>
       </c>
-      <c r="Y70" t="s">
+      <c r="Z70" t="s">
         <v>256</v>
       </c>
-      <c r="Z70" t="s">
+      <c r="AA70" t="s">
         <v>48</v>
       </c>
-      <c r="AA70" t="s">
+      <c r="AB70" t="s">
         <v>260</v>
       </c>
-      <c r="AB70" s="5">
+      <c r="AC70" s="5">
         <v>45698</v>
       </c>
-      <c r="AC70" s="12" t="s">
+      <c r="AD70" s="5"/>
+      <c r="AE70" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="AD70" s="12" t="s">
+      <c r="AF70" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="AE70" t="s">
+      <c r="AG70" t="s">
         <v>48</v>
       </c>
-      <c r="AF70" t="s">
+      <c r="AH70" t="s">
         <v>329</v>
       </c>
-      <c r="AG70" t="str">
+      <c r="AI70" t="str">
         <f t="shared" si="2"/>
         <v>MC_WR (mg/kg)</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>229</v>
       </c>
@@ -6964,7 +7138,7 @@
       <c r="O71" t="s">
         <v>249</v>
       </c>
-      <c r="P71" s="21"/>
+      <c r="P71" s="20"/>
       <c r="Q71" s="4" t="s">
         <v>337</v>
       </c>
@@ -6974,42 +7148,45 @@
       <c r="S71" t="s">
         <v>248</v>
       </c>
-      <c r="T71" t="s">
+      <c r="U71" t="s">
         <v>229</v>
       </c>
-      <c r="X71" t="s">
+      <c r="Y71" t="s">
         <v>229</v>
       </c>
-      <c r="Y71" t="s">
+      <c r="Z71" t="s">
         <v>264</v>
       </c>
-      <c r="Z71" t="s">
+      <c r="AA71" t="s">
         <v>48</v>
       </c>
-      <c r="AA71" t="s">
+      <c r="AB71" t="s">
         <v>265</v>
       </c>
-      <c r="AB71" s="5">
+      <c r="AC71" s="5">
         <v>45698</v>
       </c>
-      <c r="AC71" s="12" t="s">
+      <c r="AD71" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="AE71" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="AD71" s="12" t="s">
+      <c r="AF71" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="AE71" t="s">
+      <c r="AG71" t="s">
         <v>48</v>
       </c>
-      <c r="AF71" t="s">
+      <c r="AH71" t="s">
         <v>329</v>
       </c>
-      <c r="AG71" t="str">
+      <c r="AI71" t="str">
         <f t="shared" si="2"/>
         <v>MC_YR (mg/kg)</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>226</v>
       </c>
@@ -7028,7 +7205,7 @@
       <c r="O72" t="s">
         <v>267</v>
       </c>
-      <c r="P72" s="21"/>
+      <c r="P72" s="20"/>
       <c r="Q72" s="4" t="s">
         <v>337</v>
       </c>
@@ -7038,82 +7215,85 @@
       <c r="S72" t="s">
         <v>266</v>
       </c>
-      <c r="T72" t="s">
+      <c r="U72" t="s">
         <v>305</v>
       </c>
-      <c r="X72" t="s">
+      <c r="Y72" t="s">
         <v>305</v>
       </c>
-      <c r="Y72" t="s">
+      <c r="Z72" t="s">
         <v>306</v>
       </c>
-      <c r="Z72" s="3" t="s">
+      <c r="AA72" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AA72" s="20" t="s">
+      <c r="AB72" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="AB72" s="5">
+      <c r="AC72" s="5">
         <v>45700</v>
       </c>
-      <c r="AC72" s="12" t="s">
+      <c r="AD72" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="AE72" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="AD72" s="12" t="s">
+      <c r="AF72" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="AE72" t="s">
+      <c r="AG72" t="s">
         <v>48</v>
       </c>
-      <c r="AF72" t="s">
+      <c r="AH72" t="s">
         <v>329</v>
       </c>
-      <c r="AG72" t="str">
+      <c r="AI72" t="str">
         <f t="shared" si="2"/>
         <v>NOD_R (mg/kg)</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG72" xr:uid="{604718B0-4585-451D-AFD3-6923AD565DA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC51">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE51">
     <sortCondition ref="A2:A51"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="S41" r:id="rId1" xr:uid="{1626B51C-1015-4732-A4E4-DD5A79875C36}"/>
-    <hyperlink ref="AA7" r:id="rId2" xr:uid="{70A67022-9547-4C39-A96D-FABB76B65A5E}"/>
-    <hyperlink ref="AA9" r:id="rId3" xr:uid="{338342D9-68AD-44D3-95C3-16C92EABD5BF}"/>
-    <hyperlink ref="AA11" r:id="rId4" xr:uid="{D6CD074A-48D2-4C95-9DA6-864DF2F27C95}"/>
-    <hyperlink ref="AA12" r:id="rId5" xr:uid="{089377B3-6BA8-44DA-AAF2-6EE4C9DAA818}"/>
-    <hyperlink ref="AA13" r:id="rId6" xr:uid="{894BC872-CF08-4B37-BDA4-7208B6DFE767}"/>
-    <hyperlink ref="AA16" r:id="rId7" xr:uid="{C25B200F-9D87-493A-BFAF-A5F6605142B9}"/>
-    <hyperlink ref="AA17" r:id="rId8" xr:uid="{1CD0AC49-BF3F-469E-9D8D-D64831CC7947}"/>
-    <hyperlink ref="AA18" r:id="rId9" xr:uid="{A754AACD-1A70-424C-BFF3-63412AD44A72}"/>
-    <hyperlink ref="AA21" r:id="rId10" xr:uid="{CF186C46-85F4-42ED-BE9D-AF0FF74997D7}"/>
-    <hyperlink ref="AA25" r:id="rId11" xr:uid="{2EABFE79-AA6A-48BB-A55E-6C20A4CD78E5}"/>
-    <hyperlink ref="AA27" r:id="rId12" xr:uid="{0166E27D-3BBB-4F2B-BB14-BC302E63B65C}"/>
-    <hyperlink ref="AA29" r:id="rId13" xr:uid="{A9BFC1A7-562B-4325-96EA-E00B56121E33}"/>
-    <hyperlink ref="AA35" r:id="rId14" xr:uid="{D1A5DA3D-3C06-46B2-B4A0-C342DD14257E}"/>
-    <hyperlink ref="AA37" r:id="rId15" xr:uid="{8E49C39A-8AA2-495D-A606-02312E151058}"/>
-    <hyperlink ref="AA39" r:id="rId16" xr:uid="{145EDD2C-4AF7-4FD0-944A-020240EF92F6}"/>
-    <hyperlink ref="AA43" r:id="rId17" xr:uid="{BCBC1436-4A29-4D29-B0AF-64FBE2F2A4D4}"/>
-    <hyperlink ref="AA45" r:id="rId18" xr:uid="{998D1598-EEC0-4042-AB2F-6C8C44BF87E6}"/>
-    <hyperlink ref="AA46" r:id="rId19" xr:uid="{32A8714D-4150-4026-8256-6CA550C433CE}"/>
-    <hyperlink ref="AA47" r:id="rId20" xr:uid="{5B56A2D9-5FF3-450F-83A0-7C132F09FB8A}"/>
-    <hyperlink ref="AA48" r:id="rId21" xr:uid="{62F90194-023F-425E-A74B-E7FCB8366E8B}"/>
-    <hyperlink ref="AA49" r:id="rId22" xr:uid="{250E5402-1293-4C16-AFAC-DD56E8828484}"/>
-    <hyperlink ref="AA50" r:id="rId23" xr:uid="{7BD81D4B-6310-4C49-80EC-66BE67C6A0F3}"/>
-    <hyperlink ref="AA54" r:id="rId24" xr:uid="{8E3C2FF3-A439-432D-A392-71DA91D6B4D0}"/>
-    <hyperlink ref="AA55" r:id="rId25" xr:uid="{E18997DE-5A2F-4CDF-A366-F84437621544}"/>
-    <hyperlink ref="AA57" r:id="rId26" xr:uid="{3FEBF57F-3680-4142-AFB5-9493FBB36403}"/>
-    <hyperlink ref="AA59" r:id="rId27" xr:uid="{D90DDEA1-B31C-48B7-A511-C1F0B28339CE}"/>
-    <hyperlink ref="AA60" r:id="rId28" xr:uid="{870F7CF8-C8C6-4CEB-9B21-237AB49EE5CE}"/>
-    <hyperlink ref="AA61" r:id="rId29" xr:uid="{9EC50DF2-B5B4-4CDA-8EA4-3942DCE2067A}"/>
-    <hyperlink ref="AA62" r:id="rId30" xr:uid="{C32A3405-77ED-45FE-8E14-E0B62987621F}"/>
-    <hyperlink ref="AA72" r:id="rId31" xr:uid="{E16B3489-85E3-4DFE-813B-62540016F9AB}"/>
-    <hyperlink ref="AA3" r:id="rId32" xr:uid="{5811A01D-DC24-4AE4-A4A4-BF11336B3BFD}"/>
+    <hyperlink ref="AB7" r:id="rId2" xr:uid="{F28E2579-E2A8-435E-A2AD-ADC9FD8542D6}"/>
+    <hyperlink ref="AB9" r:id="rId3" xr:uid="{0EAB3E9D-003F-44F6-B03A-26627B342651}"/>
+    <hyperlink ref="AB11" r:id="rId4" xr:uid="{39378CF1-9776-4E8D-9AC6-977BA6B5B251}"/>
+    <hyperlink ref="AB12" r:id="rId5" xr:uid="{15AC88DA-3EFE-4D1D-A601-915E875D3F0F}"/>
+    <hyperlink ref="AB13" r:id="rId6" xr:uid="{3DADBD29-C730-4C52-839A-DE2241CECDD2}"/>
+    <hyperlink ref="AB16" r:id="rId7" xr:uid="{0CD87C6A-D210-4B37-904F-A773D188C394}"/>
+    <hyperlink ref="AB17" r:id="rId8" xr:uid="{BCE7E99D-81CC-40BC-82A2-C25415323299}"/>
+    <hyperlink ref="AB18" r:id="rId9" xr:uid="{98B6DAE2-16FE-45E0-8C16-829E374BFB96}"/>
+    <hyperlink ref="AB21" r:id="rId10" xr:uid="{CE570CC5-0527-4E3F-AC87-FCCECE22552C}"/>
+    <hyperlink ref="AB25" r:id="rId11" xr:uid="{4F518F33-05BB-4A8F-9FFC-E4EFC8375361}"/>
+    <hyperlink ref="AB27" r:id="rId12" xr:uid="{131B9BC4-299A-4FBD-9194-2D2D4BFB0997}"/>
+    <hyperlink ref="AB29" r:id="rId13" xr:uid="{41A83264-0EB2-4543-A46D-2F4B0862C237}"/>
+    <hyperlink ref="AB35" r:id="rId14" xr:uid="{8C44F00C-78C9-4B81-B779-8B5251BEB7E1}"/>
+    <hyperlink ref="AB37" r:id="rId15" xr:uid="{A2C3642C-4B2D-4A90-86D0-EAF0BAF8BC59}"/>
+    <hyperlink ref="AB39" r:id="rId16" xr:uid="{2E6A56ED-8CCC-4B33-AF8B-F3FEC2A627EF}"/>
+    <hyperlink ref="AB43" r:id="rId17" xr:uid="{E62B622B-11F4-4134-A05A-0445DB56B304}"/>
+    <hyperlink ref="AB45" r:id="rId18" xr:uid="{081F4728-351D-4701-A88F-A7B6700527EF}"/>
+    <hyperlink ref="AB46" r:id="rId19" xr:uid="{E27BD646-68D4-4592-90E3-7F06996571C2}"/>
+    <hyperlink ref="AB47" r:id="rId20" xr:uid="{01F71EBC-5A66-4E85-974B-CAFA21916719}"/>
+    <hyperlink ref="AB48" r:id="rId21" xr:uid="{16E5252D-CE04-4304-9F4C-B458D0E0B781}"/>
+    <hyperlink ref="AB49" r:id="rId22" xr:uid="{41ADB5C9-B807-4C0D-BC2E-F1011FD23FC9}"/>
+    <hyperlink ref="AB50" r:id="rId23" xr:uid="{76811145-F44C-475E-95DC-0078FB2681D2}"/>
+    <hyperlink ref="AB54" r:id="rId24" xr:uid="{1F09F5C5-3266-41AB-A81E-C7E63E056A14}"/>
+    <hyperlink ref="AB55" r:id="rId25" xr:uid="{18A84AB5-8C7D-49FA-830A-B593DF069531}"/>
+    <hyperlink ref="AB57" r:id="rId26" xr:uid="{931D7621-99F8-4727-9448-D3F333B84010}"/>
+    <hyperlink ref="AB59" r:id="rId27" xr:uid="{AEC7B0D6-94B0-4325-87FF-EB35411208C2}"/>
+    <hyperlink ref="AB60" r:id="rId28" xr:uid="{9099387E-27DF-4A20-8E5B-75D3317970FE}"/>
+    <hyperlink ref="AB61" r:id="rId29" xr:uid="{80F4F414-463C-4FB1-949F-A3F57BF135CF}"/>
+    <hyperlink ref="AB62" r:id="rId30" xr:uid="{93A63D2D-35C7-4DB9-8400-78570844FBF6}"/>
+    <hyperlink ref="AB72" r:id="rId31" xr:uid="{04A16CA8-8B48-448A-904A-117642E39DD3}"/>
+    <hyperlink ref="AB3" r:id="rId32" xr:uid="{24AC84FF-1503-45F3-923F-117EF975EA33}"/>
+    <hyperlink ref="AB68" r:id="rId33" xr:uid="{C5464080-36A2-4DA1-93D3-863C42546752}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>
--- a/config/lista_toxiner.xlsx
+++ b/config/lista_toxiner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\SLV-Biotoxin-Validator-App\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5DA811-D6B1-482B-AB9C-E7AF0AA9B08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6FF349-F9B4-4DCA-A28A-C76455476E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="0" windowWidth="25820" windowHeight="13900" xr2:uid="{5EE10D2C-8E1B-4393-ADF2-C1365B6C7898}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="420">
   <si>
     <t>Enhet</t>
   </si>
@@ -1299,6 +1299,9 @@
   </si>
   <si>
     <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004059/</t>
+  </si>
+  <si>
+    <t>https://vocab.nerc.ac.uk/collection/S27/current/CS004014/</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1454,6 +1457,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
@@ -3165,7 +3169,9 @@
       <c r="AC16" s="5">
         <v>45691</v>
       </c>
-      <c r="AD16" s="5"/>
+      <c r="AD16" s="24" t="s">
+        <v>419</v>
+      </c>
       <c r="AE16" s="12" t="s">
         <v>93</v>
       </c>
@@ -7292,8 +7298,9 @@
     <hyperlink ref="AB72" r:id="rId31" xr:uid="{04A16CA8-8B48-448A-904A-117642E39DD3}"/>
     <hyperlink ref="AB3" r:id="rId32" xr:uid="{24AC84FF-1503-45F3-923F-117EF975EA33}"/>
     <hyperlink ref="AB68" r:id="rId33" xr:uid="{C5464080-36A2-4DA1-93D3-863C42546752}"/>
+    <hyperlink ref="AD16" r:id="rId34" xr:uid="{2780E62E-742D-4138-A978-F8553DC8D3E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>